--- a/nr-doc-core-service-request/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/nr-doc-core-service-request/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T16:19:33+00:00</t>
+    <t>2026-06-15T16:22:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/nr-doc-core-service-request/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T16:22:03+00:00</t>
+    <t>2026-06-22T07:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/nr-doc-core-service-request/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T07:18:24+00:00</t>
+    <t>2026-07-23T09:21:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/nr-doc-core-service-request/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:21:02+00:00</t>
+    <t>2026-07-23T09:32:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/nr-doc-core-service-request/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:32:23+00:00</t>
+    <t>2026-07-23T09:36:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/nr-doc-core-service-request/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:36:51+00:00</t>
+    <t>2026-07-23T09:46:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/nr-doc-core-service-request/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:46:12+00:00</t>
+    <t>2026-07-23T09:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/nr-doc-core-service-request/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:54:31+00:00</t>
+    <t>2026-07-23T10:00:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/nr-doc-core-service-request/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T10:00:41+00:00</t>
+    <t>2026-07-31T09:43:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/nr-doc-core-service-request/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T09:43:50+00:00</t>
+    <t>2026-07-31T14:55:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
